--- a/saft-gt-evaluation_rawdata.xlsx
+++ b/saft-gt-evaluation_rawdata.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5DD04B-CD1F-4417-86AC-FE091141CF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1CC566-F1D3-468E-8829-1E29ECD41CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="safesec_data" sheetId="1" r:id="rId1"/>
@@ -1319,7 +1319,7 @@
         <v>844.79163135542615</v>
       </c>
       <c r="P4" s="5">
-        <f t="shared" ref="P4:S4" si="1">AVERAGE(P8:P107)</f>
+        <f t="shared" ref="P4:R4" si="1">AVERAGE(P8:P107)</f>
         <v>17.61858811004786</v>
       </c>
       <c r="Q4" s="4">
@@ -1335,7 +1335,7 @@
         <v>852.16029497255431</v>
       </c>
       <c r="T4" s="5">
-        <f t="shared" ref="T4:W4" si="2">AVERAGE(T8:T107)</f>
+        <f t="shared" ref="T4:V4" si="2">AVERAGE(T8:T107)</f>
         <v>21.70818108077161</v>
       </c>
       <c r="U4" s="4">
@@ -1419,55 +1419,55 @@
         <v>29</v>
       </c>
       <c r="B6" s="4">
-        <f>STDEV(B8:B107)</f>
+        <f t="shared" ref="B6:N6" si="3">STDEV(B8:B107)</f>
         <v>0.97479863551901247</v>
       </c>
       <c r="C6" s="4">
-        <f>STDEV(C8:C107)</f>
+        <f t="shared" si="3"/>
         <v>8.5806002427845501E-3</v>
       </c>
       <c r="D6" s="4">
-        <f>STDEV(D8:D107)</f>
+        <f t="shared" si="3"/>
         <v>2.1876632864803471E-3</v>
       </c>
       <c r="E6" s="3">
-        <f>STDEV(E8:E107)</f>
+        <f t="shared" si="3"/>
         <v>0.30682571430857758</v>
       </c>
       <c r="F6" s="4">
-        <f>STDEV(F8:F107)</f>
+        <f t="shared" si="3"/>
         <v>8.8442212161136402E-2</v>
       </c>
       <c r="G6" s="3">
-        <f>STDEV(G8:G107)</f>
+        <f t="shared" si="3"/>
         <v>0.73762148393564131</v>
       </c>
       <c r="H6" s="4">
-        <f>STDEV(H8:H107)</f>
+        <f t="shared" si="3"/>
         <v>2.6962478714155453E-3</v>
       </c>
       <c r="I6" s="4">
-        <f>STDEV(I8:I107)</f>
+        <f t="shared" si="3"/>
         <v>0.87856319557008189</v>
       </c>
       <c r="J6" s="4">
-        <f>STDEV(J8:J107)</f>
+        <f t="shared" si="3"/>
         <v>0.66243205485727752</v>
       </c>
       <c r="K6" s="3">
-        <f>STDEV(K8:K107)</f>
+        <f t="shared" si="3"/>
         <v>0.95569109813096542</v>
       </c>
       <c r="L6" s="5">
-        <f>STDEV(L8:L107)</f>
+        <f t="shared" si="3"/>
         <v>1.0751945334298472</v>
       </c>
       <c r="M6" s="4">
-        <f>STDEV(M8:M107)</f>
+        <f t="shared" si="3"/>
         <v>0.26667911140056716</v>
       </c>
       <c r="N6" s="3">
-        <f>STDEV(N8:N107)</f>
+        <f t="shared" si="3"/>
         <v>4.1028009994668636E-2</v>
       </c>
       <c r="O6" s="5">
